--- a/PAMF_DIG F2 - monthly2026-07-14.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-14.xlsx
@@ -8663,7 +8663,7 @@
         <v>0.09</v>
       </c>
       <c r="N113" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>0.09</v>
       </c>
       <c r="N135" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>0.09</v>
       </c>
       <c r="N176" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>0.09</v>
       </c>
       <c r="N222" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>0.09</v>
       </c>
       <c r="N240" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
